--- a/output/topology_excel/4862.xlsx
+++ b/output/topology_excel/4862.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,10 +506,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -531,7 +531,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B7" t="n">
         <v>9</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -616,10 +616,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>5</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -660,10 +660,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -685,7 +685,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -696,10 +696,10 @@
         <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="F12" t="n">
-        <v>136</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -707,7 +707,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -718,10 +718,10 @@
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="F13" t="n">
-        <v>56</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
@@ -729,7 +729,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -740,19 +740,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>433</v>
+        <v>177</v>
       </c>
       <c r="F14" t="n">
-        <v>218</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" t="n">
         <v>2</v>
       </c>
-      <c r="B15" t="n">
-        <v>3</v>
-      </c>
       <c r="C15" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -762,18 +762,18 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>129</v>
+        <v>187</v>
       </c>
       <c r="F15" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -784,18 +784,18 @@
         <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>286</v>
+        <v>420</v>
       </c>
       <c r="F16" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -806,18 +806,18 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>124</v>
+        <v>193</v>
       </c>
       <c r="F17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B18" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -828,18 +828,18 @@
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>177</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -850,18 +850,18 @@
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>171</v>
+        <v>323</v>
       </c>
       <c r="F19" t="n">
-        <v>43</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -872,18 +872,18 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>210</v>
+        <v>171</v>
       </c>
       <c r="F20" t="n">
-        <v>151</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -894,18 +894,18 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="F21" t="n">
-        <v>157</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -916,19 +916,19 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>377</v>
+        <v>244</v>
       </c>
       <c r="F22" t="n">
-        <v>339</v>
+        <v>243</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" t="n">
         <v>5</v>
       </c>
-      <c r="B23" t="n">
-        <v>11</v>
-      </c>
       <c r="C23" t="inlineStr">
         <is>
           <t>Wall</t>
@@ -938,18 +938,18 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>244</v>
+        <v>98</v>
       </c>
       <c r="F23" t="n">
-        <v>243</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>420</v>
+        <v>364</v>
       </c>
       <c r="F24" t="n">
-        <v>214</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25">
@@ -971,7 +971,7 @@
         <v>5</v>
       </c>
       <c r="B25" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -982,18 +982,18 @@
         <v>1</v>
       </c>
       <c r="E25" t="n">
-        <v>250</v>
+        <v>193</v>
       </c>
       <c r="F25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -1004,18 +1004,18 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="F26" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1026,18 +1026,18 @@
         <v>1</v>
       </c>
       <c r="E27" t="n">
-        <v>37</v>
+        <v>214</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B28" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1048,18 +1048,18 @@
         <v>1</v>
       </c>
       <c r="E28" t="n">
-        <v>277</v>
+        <v>253</v>
       </c>
       <c r="F28" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -1070,18 +1070,18 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>346</v>
+        <v>169</v>
       </c>
       <c r="F29" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B30" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -1095,15 +1095,15 @@
         <v>139</v>
       </c>
       <c r="F30" t="n">
-        <v>14</v>
+        <v>136</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B31" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1114,18 +1114,18 @@
         <v>1</v>
       </c>
       <c r="E31" t="n">
-        <v>193</v>
+        <v>129</v>
       </c>
       <c r="F31" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1136,18 +1136,18 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>102</v>
+        <v>286</v>
       </c>
       <c r="F32" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1158,18 +1158,18 @@
         <v>1</v>
       </c>
       <c r="E33" t="n">
-        <v>461</v>
+        <v>176</v>
       </c>
       <c r="F33" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B34" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1180,32 +1180,230 @@
         <v>1</v>
       </c>
       <c r="E34" t="n">
-        <v>253</v>
+        <v>139</v>
       </c>
       <c r="F34" t="n">
-        <v>45</v>
+        <v>14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
+        <v>8</v>
+      </c>
+      <c r="B35" t="n">
+        <v>9</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
+        <v>151</v>
+      </c>
+      <c r="F35" t="n">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>9</v>
+      </c>
+      <c r="B36" t="n">
+        <v>10</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>250</v>
+      </c>
+      <c r="F36" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>11</v>
+      </c>
+      <c r="B37" t="n">
+        <v>16</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>171</v>
+      </c>
+      <c r="F37" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>11</v>
+      </c>
+      <c r="B38" t="n">
+        <v>17</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>37</v>
+      </c>
+      <c r="F38" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>11</v>
+      </c>
+      <c r="B39" t="n">
         <v>13</v>
       </c>
-      <c r="B35" t="n">
-        <v>14</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Wall</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="n">
-        <v>169</v>
-      </c>
-      <c r="F35" t="n">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>277</v>
+      </c>
+      <c r="F39" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>13</v>
+      </c>
+      <c r="B40" t="n">
+        <v>17</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>461</v>
+      </c>
+      <c r="F40" t="n">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
         <v>16</v>
+      </c>
+      <c r="B41" t="n">
+        <v>17</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>346</v>
+      </c>
+      <c r="F41" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>1</v>
+      </c>
+      <c r="B42" t="n">
+        <v>2</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>341</v>
+      </c>
+      <c r="F42" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" t="n">
+        <v>3</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>128</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2</v>
+      </c>
+      <c r="B44" t="n">
+        <v>9</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>211</v>
+      </c>
+      <c r="F44" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/4862.xlsx
+++ b/output/topology_excel/4862.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,22 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
         </is>
       </c>
     </row>
@@ -481,6 +491,8 @@
       <c r="F2" t="n">
         <v>20</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +515,8 @@
       <c r="F3" t="n">
         <v>10</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +539,8 @@
       <c r="F4" t="n">
         <v>17</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +563,8 @@
       <c r="F5" t="n">
         <v>13</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +587,8 @@
       <c r="F6" t="n">
         <v>17</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +611,8 @@
       <c r="F7" t="n">
         <v>12</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -613,6 +635,8 @@
       <c r="F8" t="n">
         <v>18</v>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +659,8 @@
       <c r="F9" t="n">
         <v>16</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +683,8 @@
       <c r="F10" t="n">
         <v>16</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +707,8 @@
       <c r="F11" t="n">
         <v>11</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +731,8 @@
       <c r="F12" t="n">
         <v>13</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +755,8 @@
       <c r="F13" t="n">
         <v>13</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +779,8 @@
       <c r="F14" t="n">
         <v>20</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +803,8 @@
       <c r="F15" t="n">
         <v>13</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -787,8 +825,10 @@
         <v>420</v>
       </c>
       <c r="F16" t="n">
-        <v>53</v>
-      </c>
+        <v>22</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -811,6 +851,8 @@
       <c r="F17" t="n">
         <v>12</v>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -833,6 +875,8 @@
       <c r="F18" t="n">
         <v>12</v>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -855,6 +899,8 @@
       <c r="F19" t="n">
         <v>13</v>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -877,6 +923,8 @@
       <c r="F20" t="n">
         <v>43</v>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -899,6 +947,8 @@
       <c r="F21" t="n">
         <v>17</v>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -913,13 +963,19 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>244</v>
+        <v>200</v>
       </c>
       <c r="F22" t="n">
-        <v>243</v>
+        <v>43</v>
+      </c>
+      <c r="G22" t="n">
+        <v>201</v>
+      </c>
+      <c r="H22" t="n">
+        <v>43</v>
       </c>
     </row>
     <row r="23">
@@ -941,8 +997,10 @@
         <v>98</v>
       </c>
       <c r="F23" t="n">
-        <v>95</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -965,6 +1023,8 @@
       <c r="F24" t="n">
         <v>16</v>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -987,6 +1047,8 @@
       <c r="F25" t="n">
         <v>12</v>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1009,6 +1071,8 @@
       <c r="F26" t="n">
         <v>12</v>
       </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1031,6 +1095,8 @@
       <c r="F27" t="n">
         <v>16</v>
       </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1053,6 +1119,8 @@
       <c r="F28" t="n">
         <v>45</v>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1075,6 +1143,8 @@
       <c r="F29" t="n">
         <v>16</v>
       </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1089,13 +1159,19 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F30" t="n">
-        <v>136</v>
+        <v>9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>127</v>
+      </c>
+      <c r="H30" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="31">
@@ -1119,6 +1195,8 @@
       <c r="F31" t="n">
         <v>17</v>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1141,6 +1219,8 @@
       <c r="F32" t="n">
         <v>20</v>
       </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1155,13 +1235,19 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="F33" t="n">
-        <v>56</v>
+        <v>17</v>
+      </c>
+      <c r="G33" t="n">
+        <v>39</v>
+      </c>
+      <c r="H33" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="34">
@@ -1185,6 +1271,8 @@
       <c r="F34" t="n">
         <v>14</v>
       </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1199,13 +1287,19 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="F35" t="n">
-        <v>39</v>
+        <v>12</v>
+      </c>
+      <c r="G35" t="n">
+        <v>27</v>
+      </c>
+      <c r="H35" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="36">
@@ -1229,6 +1323,8 @@
       <c r="F36" t="n">
         <v>11</v>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1251,6 +1347,8 @@
       <c r="F37" t="n">
         <v>37</v>
       </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1273,6 +1371,8 @@
       <c r="F38" t="n">
         <v>24</v>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1295,6 +1395,8 @@
       <c r="F39" t="n">
         <v>19</v>
       </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1317,6 +1419,8 @@
       <c r="F40" t="n">
         <v>37</v>
       </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1339,6 +1443,8 @@
       <c r="F41" t="n">
         <v>18</v>
       </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1361,6 +1467,8 @@
       <c r="F42" t="n">
         <v>18</v>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1383,6 +1491,8 @@
       <c r="F43" t="n">
         <v>1</v>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1405,6 +1515,8 @@
       <c r="F44" t="n">
         <v>2</v>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
